--- a/ratings_mean_clean.xlsx
+++ b/ratings_mean_clean.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="13">
   <si>
     <t>Year</t>
   </si>
@@ -410,7 +410,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C220"/>
+  <dimension ref="A1:C245"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -700,6 +700,9 @@
       <c r="B27" t="s">
         <v>4</v>
       </c>
+      <c r="C27">
+        <v>5</v>
+      </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
@@ -709,7 +712,7 @@
         <v>4</v>
       </c>
       <c r="C28">
-        <v>4</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -719,6 +722,9 @@
       <c r="B29" t="s">
         <v>4</v>
       </c>
+      <c r="C29">
+        <v>6</v>
+      </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
@@ -761,7 +767,7 @@
         <v>4</v>
       </c>
       <c r="C33">
-        <v>4</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -771,6 +777,9 @@
       <c r="B34" t="s">
         <v>4</v>
       </c>
+      <c r="C34">
+        <v>3.5</v>
+      </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
@@ -779,6 +788,9 @@
       <c r="B35" t="s">
         <v>4</v>
       </c>
+      <c r="C35">
+        <v>6</v>
+      </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
@@ -787,6 +799,9 @@
       <c r="B36" t="s">
         <v>4</v>
       </c>
+      <c r="C36">
+        <v>6</v>
+      </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
@@ -803,6 +818,9 @@
       <c r="B38" t="s">
         <v>4</v>
       </c>
+      <c r="C38">
+        <v>7</v>
+      </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
@@ -811,6 +829,9 @@
       <c r="B39" t="s">
         <v>4</v>
       </c>
+      <c r="C39">
+        <v>6.5</v>
+      </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
@@ -819,6 +840,9 @@
       <c r="B40" t="s">
         <v>4</v>
       </c>
+      <c r="C40">
+        <v>7</v>
+      </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
@@ -827,6 +851,9 @@
       <c r="B41" t="s">
         <v>4</v>
       </c>
+      <c r="C41">
+        <v>6.5</v>
+      </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
@@ -835,6 +862,9 @@
       <c r="B42" t="s">
         <v>4</v>
       </c>
+      <c r="C42">
+        <v>7</v>
+      </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
@@ -1212,7 +1242,7 @@
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>2005</v>
+        <v>2001</v>
       </c>
       <c r="B77" t="s">
         <v>6</v>
@@ -1223,7 +1253,7 @@
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>2011</v>
+        <v>2002</v>
       </c>
       <c r="B78" t="s">
         <v>6</v>
@@ -1234,678 +1264,678 @@
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>2012</v>
+        <v>2003</v>
       </c>
       <c r="B79" t="s">
         <v>6</v>
       </c>
       <c r="C79">
-        <v>20.33333333333333</v>
+        <v>21</v>
       </c>
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>2013</v>
+        <v>2004</v>
       </c>
       <c r="B80" t="s">
         <v>6</v>
       </c>
       <c r="C80">
-        <v>19.5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>2014</v>
+        <v>2005</v>
       </c>
       <c r="B81" t="s">
         <v>6</v>
       </c>
       <c r="C81">
-        <v>19.5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>2015</v>
+        <v>2006</v>
       </c>
       <c r="B82" t="s">
         <v>6</v>
       </c>
       <c r="C82">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="83" spans="1:3">
       <c r="A83">
-        <v>2016</v>
+        <v>2007</v>
       </c>
       <c r="B83" t="s">
         <v>6</v>
       </c>
       <c r="C83">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="84" spans="1:3">
       <c r="A84">
-        <v>2017</v>
+        <v>2008</v>
       </c>
       <c r="B84" t="s">
         <v>6</v>
       </c>
       <c r="C84">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85">
-        <v>2018</v>
+        <v>2009</v>
       </c>
       <c r="B85" t="s">
         <v>6</v>
       </c>
       <c r="C85">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="86" spans="1:3">
       <c r="A86">
-        <v>2019</v>
+        <v>2010</v>
       </c>
       <c r="B86" t="s">
         <v>6</v>
       </c>
       <c r="C86">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="87" spans="1:3">
       <c r="A87">
-        <v>2020</v>
+        <v>2011</v>
       </c>
       <c r="B87" t="s">
         <v>6</v>
       </c>
       <c r="C87">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="88" spans="1:3">
       <c r="A88">
-        <v>2021</v>
+        <v>2012</v>
       </c>
       <c r="B88" t="s">
         <v>6</v>
       </c>
       <c r="C88">
-        <v>19</v>
+        <v>20.33333333333333</v>
       </c>
     </row>
     <row r="89" spans="1:3">
       <c r="A89">
-        <v>2022</v>
+        <v>2013</v>
       </c>
       <c r="B89" t="s">
         <v>6</v>
       </c>
       <c r="C89">
-        <v>19</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="90" spans="1:3">
       <c r="A90">
-        <v>2023</v>
+        <v>2014</v>
       </c>
       <c r="B90" t="s">
         <v>6</v>
       </c>
       <c r="C90">
-        <v>18</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="91" spans="1:3">
       <c r="A91">
-        <v>2024</v>
+        <v>2015</v>
       </c>
       <c r="B91" t="s">
         <v>6</v>
       </c>
       <c r="C91">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="92" spans="1:3">
       <c r="A92">
-        <v>2025</v>
+        <v>2016</v>
       </c>
       <c r="B92" t="s">
         <v>6</v>
       </c>
       <c r="C92">
-        <v>17.33333333333333</v>
+        <v>19</v>
       </c>
     </row>
     <row r="93" spans="1:3">
       <c r="A93">
-        <v>2000</v>
+        <v>2017</v>
       </c>
       <c r="B93" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C93">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="94" spans="1:3">
       <c r="A94">
-        <v>2001</v>
+        <v>2018</v>
       </c>
       <c r="B94" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C94">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="95" spans="1:3">
       <c r="A95">
-        <v>2002</v>
+        <v>2019</v>
       </c>
       <c r="B95" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C95">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="96" spans="1:3">
       <c r="A96">
-        <v>2003</v>
+        <v>2020</v>
       </c>
       <c r="B96" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C96">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="97" spans="1:3">
       <c r="A97">
-        <v>2004</v>
+        <v>2021</v>
       </c>
       <c r="B97" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C97">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="98" spans="1:3">
       <c r="A98">
-        <v>2005</v>
+        <v>2022</v>
       </c>
       <c r="B98" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C98">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="99" spans="1:3">
       <c r="A99">
-        <v>2007</v>
+        <v>2023</v>
       </c>
       <c r="B99" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C99">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="100" spans="1:3">
       <c r="A100">
-        <v>2008</v>
+        <v>2024</v>
       </c>
       <c r="B100" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C100">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="101" spans="1:3">
       <c r="A101">
-        <v>2009</v>
+        <v>2025</v>
       </c>
       <c r="B101" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C101">
-        <v>15</v>
+        <v>17.33333333333333</v>
       </c>
     </row>
     <row r="102" spans="1:3">
       <c r="A102">
-        <v>2010</v>
+        <v>2000</v>
       </c>
       <c r="B102" t="s">
         <v>7</v>
       </c>
       <c r="C102">
-        <v>11.33333333333333</v>
+        <v>15</v>
       </c>
     </row>
     <row r="103" spans="1:3">
       <c r="A103">
-        <v>2011</v>
+        <v>2001</v>
       </c>
       <c r="B103" t="s">
         <v>7</v>
       </c>
       <c r="C103">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="104" spans="1:3">
       <c r="A104">
-        <v>2012</v>
+        <v>2002</v>
       </c>
       <c r="B104" t="s">
         <v>7</v>
       </c>
       <c r="C104">
-        <v>6</v>
+        <v>16</v>
       </c>
     </row>
     <row r="105" spans="1:3">
       <c r="A105">
-        <v>2013</v>
+        <v>2003</v>
       </c>
       <c r="B105" t="s">
         <v>7</v>
       </c>
       <c r="C105">
-        <v>4.5</v>
+        <v>17</v>
       </c>
     </row>
     <row r="106" spans="1:3">
       <c r="A106">
-        <v>2014</v>
+        <v>2004</v>
       </c>
       <c r="B106" t="s">
         <v>7</v>
       </c>
       <c r="C106">
-        <v>6.333333333333333</v>
+        <v>16</v>
       </c>
     </row>
     <row r="107" spans="1:3">
       <c r="A107">
-        <v>2015</v>
+        <v>2005</v>
       </c>
       <c r="B107" t="s">
         <v>7</v>
       </c>
       <c r="C107">
-        <v>4</v>
+        <v>16</v>
       </c>
     </row>
     <row r="108" spans="1:3">
       <c r="A108">
-        <v>2016</v>
+        <v>2007</v>
       </c>
       <c r="B108" t="s">
         <v>7</v>
       </c>
       <c r="C108">
-        <v>6</v>
+        <v>16</v>
       </c>
     </row>
     <row r="109" spans="1:3">
       <c r="A109">
-        <v>2017</v>
+        <v>2008</v>
       </c>
       <c r="B109" t="s">
         <v>7</v>
       </c>
       <c r="C109">
-        <v>5.333333333333333</v>
+        <v>16</v>
       </c>
     </row>
     <row r="110" spans="1:3">
       <c r="A110">
-        <v>2018</v>
+        <v>2009</v>
       </c>
       <c r="B110" t="s">
         <v>7</v>
       </c>
       <c r="C110">
-        <v>7.666666666666667</v>
+        <v>15</v>
       </c>
     </row>
     <row r="111" spans="1:3">
       <c r="A111">
-        <v>2019</v>
+        <v>2010</v>
       </c>
       <c r="B111" t="s">
         <v>7</v>
       </c>
       <c r="C111">
-        <v>8.666666666666666</v>
+        <v>11.33333333333333</v>
       </c>
     </row>
     <row r="112" spans="1:3">
       <c r="A112">
-        <v>2020</v>
+        <v>2011</v>
       </c>
       <c r="B112" t="s">
         <v>7</v>
       </c>
       <c r="C112">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="113" spans="1:3">
       <c r="A113">
-        <v>2021</v>
+        <v>2012</v>
       </c>
       <c r="B113" t="s">
         <v>7</v>
       </c>
       <c r="C113">
-        <v>9.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="114" spans="1:3">
       <c r="A114">
-        <v>2022</v>
+        <v>2013</v>
       </c>
       <c r="B114" t="s">
         <v>7</v>
       </c>
       <c r="C114">
-        <v>9.5</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="115" spans="1:3">
       <c r="A115">
-        <v>2023</v>
+        <v>2014</v>
       </c>
       <c r="B115" t="s">
         <v>7</v>
       </c>
       <c r="C115">
-        <v>11.66666666666667</v>
+        <v>6.333333333333333</v>
       </c>
     </row>
     <row r="116" spans="1:3">
       <c r="A116">
-        <v>2024</v>
+        <v>2015</v>
       </c>
       <c r="B116" t="s">
         <v>7</v>
       </c>
       <c r="C116">
-        <v>11.5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="117" spans="1:3">
       <c r="A117">
-        <v>2025</v>
+        <v>2016</v>
       </c>
       <c r="B117" t="s">
         <v>7</v>
       </c>
       <c r="C117">
-        <v>12.33333333333333</v>
+        <v>6</v>
       </c>
     </row>
     <row r="118" spans="1:3">
       <c r="A118">
-        <v>2000</v>
+        <v>2017</v>
       </c>
       <c r="B118" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C118">
-        <v>20</v>
+        <v>5.333333333333333</v>
       </c>
     </row>
     <row r="119" spans="1:3">
       <c r="A119">
-        <v>2001</v>
+        <v>2018</v>
       </c>
       <c r="B119" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C119">
-        <v>19</v>
+        <v>7.666666666666667</v>
       </c>
     </row>
     <row r="120" spans="1:3">
       <c r="A120">
-        <v>2002</v>
+        <v>2019</v>
       </c>
       <c r="B120" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C120">
-        <v>19</v>
+        <v>8.666666666666666</v>
       </c>
     </row>
     <row r="121" spans="1:3">
       <c r="A121">
-        <v>2004</v>
+        <v>2020</v>
       </c>
       <c r="B121" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C121">
-        <v>18</v>
+        <v>10</v>
       </c>
     </row>
     <row r="122" spans="1:3">
       <c r="A122">
-        <v>2005</v>
+        <v>2021</v>
       </c>
       <c r="B122" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C122">
-        <v>18.5</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="123" spans="1:3">
       <c r="A123">
-        <v>2006</v>
+        <v>2022</v>
       </c>
       <c r="B123" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C123">
-        <v>19.5</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="124" spans="1:3">
       <c r="A124">
-        <v>2007</v>
+        <v>2023</v>
       </c>
       <c r="B124" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C124">
-        <v>20</v>
+        <v>11.66666666666667</v>
       </c>
     </row>
     <row r="125" spans="1:3">
       <c r="A125">
-        <v>2010</v>
+        <v>2024</v>
       </c>
       <c r="B125" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C125">
-        <v>19</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="126" spans="1:3">
       <c r="A126">
-        <v>2011</v>
+        <v>2025</v>
       </c>
       <c r="B126" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C126">
-        <v>18.33333333333333</v>
+        <v>12.33333333333333</v>
       </c>
     </row>
     <row r="127" spans="1:3">
       <c r="A127">
-        <v>2012</v>
+        <v>2000</v>
       </c>
       <c r="B127" t="s">
         <v>8</v>
       </c>
       <c r="C127">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="128" spans="1:3">
       <c r="A128">
-        <v>2013</v>
+        <v>2001</v>
       </c>
       <c r="B128" t="s">
         <v>8</v>
       </c>
       <c r="C128">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="129" spans="1:3">
       <c r="A129">
-        <v>2014</v>
+        <v>2002</v>
       </c>
       <c r="B129" t="s">
         <v>8</v>
       </c>
       <c r="C129">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="130" spans="1:3">
       <c r="A130">
-        <v>2015</v>
+        <v>2004</v>
       </c>
       <c r="B130" t="s">
         <v>8</v>
       </c>
       <c r="C130">
-        <v>16.5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="131" spans="1:3">
       <c r="A131">
-        <v>2016</v>
+        <v>2005</v>
       </c>
       <c r="B131" t="s">
         <v>8</v>
       </c>
       <c r="C131">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="132" spans="1:3">
       <c r="A132">
-        <v>2017</v>
+        <v>2006</v>
       </c>
       <c r="B132" t="s">
         <v>8</v>
       </c>
       <c r="C132">
-        <v>16.5</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="133" spans="1:3">
       <c r="A133">
-        <v>2018</v>
+        <v>2007</v>
       </c>
       <c r="B133" t="s">
         <v>8</v>
       </c>
       <c r="C133">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="134" spans="1:3">
       <c r="A134">
-        <v>2019</v>
+        <v>2010</v>
       </c>
       <c r="B134" t="s">
         <v>8</v>
       </c>
       <c r="C134">
-        <v>16.5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="135" spans="1:3">
       <c r="A135">
-        <v>2020</v>
+        <v>2011</v>
       </c>
       <c r="B135" t="s">
         <v>8</v>
       </c>
       <c r="C135">
-        <v>16.5</v>
+        <v>18.33333333333333</v>
       </c>
     </row>
     <row r="136" spans="1:3">
       <c r="A136">
-        <v>2021</v>
+        <v>2012</v>
       </c>
       <c r="B136" t="s">
         <v>8</v>
       </c>
       <c r="C136">
-        <v>16.5</v>
+        <v>17</v>
       </c>
     </row>
     <row r="137" spans="1:3">
       <c r="A137">
-        <v>2022</v>
+        <v>2013</v>
       </c>
       <c r="B137" t="s">
         <v>8</v>
       </c>
       <c r="C137">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="138" spans="1:3">
       <c r="A138">
-        <v>2023</v>
+        <v>2014</v>
       </c>
       <c r="B138" t="s">
         <v>8</v>
       </c>
       <c r="C138">
-        <v>16.5</v>
+        <v>17</v>
       </c>
     </row>
     <row r="139" spans="1:3">
       <c r="A139">
-        <v>2024</v>
+        <v>2015</v>
       </c>
       <c r="B139" t="s">
         <v>8</v>
       </c>
       <c r="C139">
-        <v>16</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="140" spans="1:3">
       <c r="A140">
-        <v>2025</v>
+        <v>2016</v>
       </c>
       <c r="B140" t="s">
         <v>8</v>
@@ -1916,218 +1946,200 @@
     </row>
     <row r="141" spans="1:3">
       <c r="A141">
-        <v>2000</v>
+        <v>2017</v>
       </c>
       <c r="B141" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C141">
-        <v>21</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="142" spans="1:3">
       <c r="A142">
-        <v>2005</v>
+        <v>2018</v>
       </c>
       <c r="B142" t="s">
-        <v>9</v>
+        <v>8</v>
+      </c>
+      <c r="C142">
+        <v>16.5</v>
       </c>
     </row>
     <row r="143" spans="1:3">
       <c r="A143">
-        <v>2009</v>
+        <v>2019</v>
       </c>
       <c r="B143" t="s">
-        <v>9</v>
+        <v>8</v>
+      </c>
+      <c r="C143">
+        <v>16.5</v>
       </c>
     </row>
     <row r="144" spans="1:3">
       <c r="A144">
-        <v>2010</v>
+        <v>2020</v>
       </c>
       <c r="B144" t="s">
-        <v>9</v>
+        <v>8</v>
+      </c>
+      <c r="C144">
+        <v>16.5</v>
       </c>
     </row>
     <row r="145" spans="1:3">
       <c r="A145">
-        <v>2011</v>
+        <v>2021</v>
       </c>
       <c r="B145" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C145">
-        <v>21</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="146" spans="1:3">
       <c r="A146">
-        <v>2012</v>
+        <v>2022</v>
       </c>
       <c r="B146" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C146">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
     <row r="147" spans="1:3">
       <c r="A147">
-        <v>2013</v>
+        <v>2023</v>
       </c>
       <c r="B147" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C147">
-        <v>20.0625</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="148" spans="1:3">
       <c r="A148">
-        <v>2014</v>
+        <v>2024</v>
       </c>
       <c r="B148" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C148">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="149" spans="1:3">
       <c r="A149">
-        <v>2015</v>
+        <v>2025</v>
       </c>
       <c r="B149" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C149">
-        <v>20</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="150" spans="1:3">
       <c r="A150">
-        <v>2016</v>
+        <v>2000</v>
       </c>
       <c r="B150" t="s">
         <v>9</v>
       </c>
       <c r="C150">
-        <v>19.5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="151" spans="1:3">
       <c r="A151">
-        <v>2017</v>
+        <v>2001</v>
       </c>
       <c r="B151" t="s">
         <v>9</v>
-      </c>
-      <c r="C151">
-        <v>19</v>
       </c>
     </row>
     <row r="152" spans="1:3">
       <c r="A152">
-        <v>2018</v>
+        <v>2002</v>
       </c>
       <c r="B152" t="s">
         <v>9</v>
-      </c>
-      <c r="C152">
-        <v>19</v>
       </c>
     </row>
     <row r="153" spans="1:3">
       <c r="A153">
-        <v>2019</v>
+        <v>2003</v>
       </c>
       <c r="B153" t="s">
         <v>9</v>
-      </c>
-      <c r="C153">
-        <v>19</v>
       </c>
     </row>
     <row r="154" spans="1:3">
       <c r="A154">
-        <v>2020</v>
+        <v>2004</v>
       </c>
       <c r="B154" t="s">
         <v>9</v>
-      </c>
-      <c r="C154">
-        <v>18</v>
       </c>
     </row>
     <row r="155" spans="1:3">
       <c r="A155">
-        <v>2021</v>
+        <v>2005</v>
       </c>
       <c r="B155" t="s">
         <v>9</v>
-      </c>
-      <c r="C155">
-        <v>18</v>
       </c>
     </row>
     <row r="156" spans="1:3">
       <c r="A156">
-        <v>2022</v>
+        <v>2006</v>
       </c>
       <c r="B156" t="s">
         <v>9</v>
-      </c>
-      <c r="C156">
-        <v>15</v>
       </c>
     </row>
     <row r="157" spans="1:3">
       <c r="A157">
-        <v>2023</v>
+        <v>2007</v>
       </c>
       <c r="B157" t="s">
         <v>9</v>
-      </c>
-      <c r="C157">
-        <v>18</v>
       </c>
     </row>
     <row r="158" spans="1:3">
       <c r="A158">
-        <v>2024</v>
+        <v>2008</v>
       </c>
       <c r="B158" t="s">
         <v>9</v>
-      </c>
-      <c r="C158">
-        <v>18</v>
       </c>
     </row>
     <row r="159" spans="1:3">
       <c r="A159">
-        <v>2025</v>
+        <v>2009</v>
       </c>
       <c r="B159" t="s">
         <v>9</v>
-      </c>
-      <c r="C159">
-        <v>18</v>
       </c>
     </row>
     <row r="160" spans="1:3">
       <c r="A160">
-        <v>2000</v>
+        <v>2010</v>
       </c>
       <c r="B160" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="161" spans="1:3">
       <c r="A161">
-        <v>2003</v>
+        <v>2011</v>
       </c>
       <c r="B161" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C161">
         <v>21</v>
@@ -2135,143 +2147,167 @@
     </row>
     <row r="162" spans="1:3">
       <c r="A162">
-        <v>2005</v>
+        <v>2012</v>
       </c>
       <c r="B162" t="s">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="C162">
+        <v>21</v>
       </c>
     </row>
     <row r="163" spans="1:3">
       <c r="A163">
-        <v>2011</v>
+        <v>2013</v>
       </c>
       <c r="B163" t="s">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="C163">
+        <v>20.11111111111111</v>
       </c>
     </row>
     <row r="164" spans="1:3">
       <c r="A164">
-        <v>2012</v>
+        <v>2014</v>
       </c>
       <c r="B164" t="s">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="C164">
+        <v>20</v>
       </c>
     </row>
     <row r="165" spans="1:3">
       <c r="A165">
-        <v>2013</v>
+        <v>2015</v>
       </c>
       <c r="B165" t="s">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="C165">
+        <v>20</v>
       </c>
     </row>
     <row r="166" spans="1:3">
       <c r="A166">
-        <v>2014</v>
+        <v>2016</v>
       </c>
       <c r="B166" t="s">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="C166">
+        <v>19.25</v>
       </c>
     </row>
     <row r="167" spans="1:3">
       <c r="A167">
-        <v>2015</v>
+        <v>2017</v>
       </c>
       <c r="B167" t="s">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="C167">
+        <v>19</v>
       </c>
     </row>
     <row r="168" spans="1:3">
       <c r="A168">
-        <v>2016</v>
+        <v>2018</v>
       </c>
       <c r="B168" t="s">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="C168">
+        <v>19</v>
       </c>
     </row>
     <row r="169" spans="1:3">
       <c r="A169">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="B169" t="s">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="C169">
+        <v>19</v>
       </c>
     </row>
     <row r="170" spans="1:3">
       <c r="A170">
-        <v>2018</v>
+        <v>2020</v>
       </c>
       <c r="B170" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C170">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="171" spans="1:3">
       <c r="A171">
-        <v>2019</v>
+        <v>2021</v>
       </c>
       <c r="B171" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C171">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="172" spans="1:3">
       <c r="A172">
-        <v>2020</v>
+        <v>2022</v>
       </c>
       <c r="B172" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C172">
-        <v>21</v>
+        <v>15.6</v>
       </c>
     </row>
     <row r="173" spans="1:3">
       <c r="A173">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="B173" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C173">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="174" spans="1:3">
       <c r="A174">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B174" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C174">
-        <v>20.5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="175" spans="1:3">
       <c r="A175">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B175" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C175">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="176" spans="1:3">
       <c r="A176">
-        <v>2025</v>
+        <v>2000</v>
       </c>
       <c r="B176" t="s">
         <v>10</v>
       </c>
       <c r="C176">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="177" spans="1:3">
@@ -2279,10 +2315,7 @@
         <v>2001</v>
       </c>
       <c r="B177" t="s">
-        <v>11</v>
-      </c>
-      <c r="C177">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="178" spans="1:3">
@@ -2290,348 +2323,333 @@
         <v>2002</v>
       </c>
       <c r="B178" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="179" spans="1:3">
       <c r="A179">
-        <v>2005</v>
+        <v>2003</v>
       </c>
       <c r="B179" t="s">
-        <v>11</v>
+        <v>10</v>
+      </c>
+      <c r="C179">
+        <v>21</v>
       </c>
     </row>
     <row r="180" spans="1:3">
       <c r="A180">
-        <v>2006</v>
+        <v>2004</v>
       </c>
       <c r="B180" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="181" spans="1:3">
       <c r="A181">
-        <v>2007</v>
+        <v>2005</v>
       </c>
       <c r="B181" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="182" spans="1:3">
       <c r="A182">
-        <v>2008</v>
+        <v>2006</v>
       </c>
       <c r="B182" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="183" spans="1:3">
       <c r="A183">
-        <v>2010</v>
+        <v>2007</v>
       </c>
       <c r="B183" t="s">
-        <v>11</v>
-      </c>
-      <c r="C183">
         <v>10</v>
       </c>
     </row>
     <row r="184" spans="1:3">
       <c r="A184">
-        <v>2011</v>
+        <v>2008</v>
       </c>
       <c r="B184" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="185" spans="1:3">
       <c r="A185">
-        <v>2012</v>
+        <v>2009</v>
       </c>
       <c r="B185" t="s">
-        <v>11</v>
-      </c>
-      <c r="C185">
         <v>10</v>
       </c>
     </row>
     <row r="186" spans="1:3">
       <c r="A186">
-        <v>2014</v>
+        <v>2010</v>
       </c>
       <c r="B186" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="187" spans="1:3">
       <c r="A187">
-        <v>2016</v>
+        <v>2011</v>
       </c>
       <c r="B187" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C187">
-        <v>11</v>
+        <v>21</v>
       </c>
     </row>
     <row r="188" spans="1:3">
       <c r="A188">
-        <v>2017</v>
+        <v>2012</v>
       </c>
       <c r="B188" t="s">
-        <v>11</v>
+        <v>10</v>
+      </c>
+      <c r="C188">
+        <v>21</v>
       </c>
     </row>
     <row r="189" spans="1:3">
       <c r="A189">
-        <v>2018</v>
+        <v>2013</v>
       </c>
       <c r="B189" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C189">
-        <v>10.5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="190" spans="1:3">
       <c r="A190">
-        <v>2019</v>
+        <v>2014</v>
       </c>
       <c r="B190" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C190">
-        <v>10</v>
+        <v>21</v>
       </c>
     </row>
     <row r="191" spans="1:3">
       <c r="A191">
-        <v>2020</v>
+        <v>2015</v>
       </c>
       <c r="B191" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C191">
-        <v>10</v>
+        <v>21</v>
       </c>
     </row>
     <row r="192" spans="1:3">
       <c r="A192">
-        <v>2021</v>
+        <v>2016</v>
       </c>
       <c r="B192" t="s">
-        <v>11</v>
+        <v>10</v>
+      </c>
+      <c r="C192">
+        <v>21</v>
       </c>
     </row>
     <row r="193" spans="1:3">
       <c r="A193">
-        <v>2022</v>
+        <v>2017</v>
       </c>
       <c r="B193" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C193">
-        <v>10</v>
+        <v>21</v>
       </c>
     </row>
     <row r="194" spans="1:3">
       <c r="A194">
-        <v>2023</v>
+        <v>2018</v>
       </c>
       <c r="B194" t="s">
-        <v>11</v>
+        <v>10</v>
+      </c>
+      <c r="C194">
+        <v>21</v>
       </c>
     </row>
     <row r="195" spans="1:3">
       <c r="A195">
-        <v>2024</v>
+        <v>2019</v>
       </c>
       <c r="B195" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C195">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="196" spans="1:3">
       <c r="A196">
-        <v>2025</v>
+        <v>2020</v>
       </c>
       <c r="B196" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C196">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="197" spans="1:3">
       <c r="A197">
-        <v>2000</v>
+        <v>2021</v>
       </c>
       <c r="B197" t="s">
-        <v>12</v>
-      </c>
-      <c r="C197">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="198" spans="1:3">
       <c r="A198">
-        <v>2001</v>
+        <v>2022</v>
       </c>
       <c r="B198" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C198">
-        <v>13</v>
+        <v>21</v>
       </c>
     </row>
     <row r="199" spans="1:3">
       <c r="A199">
-        <v>2002</v>
+        <v>2023</v>
       </c>
       <c r="B199" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C199">
-        <v>12</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="200" spans="1:3">
       <c r="A200">
-        <v>2003</v>
+        <v>2024</v>
       </c>
       <c r="B200" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C200">
-        <v>13</v>
+        <v>20</v>
       </c>
     </row>
     <row r="201" spans="1:3">
       <c r="A201">
-        <v>2004</v>
+        <v>2025</v>
       </c>
       <c r="B201" t="s">
-        <v>12</v>
+        <v>10</v>
+      </c>
+      <c r="C201">
+        <v>20</v>
       </c>
     </row>
     <row r="202" spans="1:3">
       <c r="A202">
-        <v>2005</v>
+        <v>2001</v>
       </c>
       <c r="B202" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C202">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="203" spans="1:3">
       <c r="A203">
-        <v>2007</v>
+        <v>2002</v>
       </c>
       <c r="B203" t="s">
-        <v>12</v>
-      </c>
-      <c r="C203">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="204" spans="1:3">
       <c r="A204">
-        <v>2008</v>
+        <v>2005</v>
       </c>
       <c r="B204" t="s">
-        <v>12</v>
-      </c>
-      <c r="C204">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="205" spans="1:3">
       <c r="A205">
-        <v>2009</v>
+        <v>2006</v>
       </c>
       <c r="B205" t="s">
-        <v>12</v>
-      </c>
-      <c r="C205">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="206" spans="1:3">
       <c r="A206">
-        <v>2011</v>
+        <v>2007</v>
       </c>
       <c r="B206" t="s">
-        <v>12</v>
-      </c>
-      <c r="C206">
-        <v>14.33333333333333</v>
+        <v>11</v>
       </c>
     </row>
     <row r="207" spans="1:3">
       <c r="A207">
-        <v>2012</v>
+        <v>2008</v>
       </c>
       <c r="B207" t="s">
-        <v>12</v>
-      </c>
-      <c r="C207">
-        <v>13.66666666666667</v>
+        <v>11</v>
       </c>
     </row>
     <row r="208" spans="1:3">
       <c r="A208">
-        <v>2013</v>
+        <v>2010</v>
       </c>
       <c r="B208" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C208">
-        <v>13.5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="209" spans="1:3">
       <c r="A209">
-        <v>2014</v>
+        <v>2011</v>
       </c>
       <c r="B209" t="s">
-        <v>12</v>
-      </c>
-      <c r="C209">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="210" spans="1:3">
       <c r="A210">
-        <v>2015</v>
+        <v>2012</v>
       </c>
       <c r="B210" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C210">
-        <v>12.33333333333333</v>
+        <v>10</v>
       </c>
     </row>
     <row r="211" spans="1:3">
       <c r="A211">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="B211" t="s">
-        <v>12</v>
-      </c>
-      <c r="C211">
-        <v>12.33333333333333</v>
+        <v>11</v>
       </c>
     </row>
     <row r="212" spans="1:3">
       <c r="A212">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="B212" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C212">
         <v>11</v>
@@ -2639,89 +2657,352 @@
     </row>
     <row r="213" spans="1:3">
       <c r="A213">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="B213" t="s">
-        <v>12</v>
-      </c>
-      <c r="C213">
-        <v>11.5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="214" spans="1:3">
       <c r="A214">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="B214" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C214">
-        <v>11</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="215" spans="1:3">
       <c r="A215">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="B215" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C215">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="216" spans="1:3">
       <c r="A216">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="B216" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C216">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="217" spans="1:3">
       <c r="A217">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B217" t="s">
-        <v>12</v>
-      </c>
-      <c r="C217">
-        <v>9.333333333333334</v>
+        <v>11</v>
       </c>
     </row>
     <row r="218" spans="1:3">
       <c r="A218">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="B218" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C218">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="219" spans="1:3">
       <c r="A219">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B219" t="s">
-        <v>12</v>
-      </c>
-      <c r="C219">
-        <v>9.5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="220" spans="1:3">
       <c r="A220">
+        <v>2024</v>
+      </c>
+      <c r="B220" t="s">
+        <v>11</v>
+      </c>
+      <c r="C220">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="221" spans="1:3">
+      <c r="A221">
         <v>2025</v>
       </c>
-      <c r="B220" t="s">
+      <c r="B221" t="s">
+        <v>11</v>
+      </c>
+      <c r="C221">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="222" spans="1:3">
+      <c r="A222">
+        <v>2000</v>
+      </c>
+      <c r="B222" t="s">
         <v>12</v>
       </c>
-      <c r="C220">
+      <c r="C222">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="223" spans="1:3">
+      <c r="A223">
+        <v>2001</v>
+      </c>
+      <c r="B223" t="s">
+        <v>12</v>
+      </c>
+      <c r="C223">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="224" spans="1:3">
+      <c r="A224">
+        <v>2002</v>
+      </c>
+      <c r="B224" t="s">
+        <v>12</v>
+      </c>
+      <c r="C224">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="225" spans="1:3">
+      <c r="A225">
+        <v>2003</v>
+      </c>
+      <c r="B225" t="s">
+        <v>12</v>
+      </c>
+      <c r="C225">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="226" spans="1:3">
+      <c r="A226">
+        <v>2004</v>
+      </c>
+      <c r="B226" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="227" spans="1:3">
+      <c r="A227">
+        <v>2005</v>
+      </c>
+      <c r="B227" t="s">
+        <v>12</v>
+      </c>
+      <c r="C227">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="228" spans="1:3">
+      <c r="A228">
+        <v>2007</v>
+      </c>
+      <c r="B228" t="s">
+        <v>12</v>
+      </c>
+      <c r="C228">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="229" spans="1:3">
+      <c r="A229">
+        <v>2008</v>
+      </c>
+      <c r="B229" t="s">
+        <v>12</v>
+      </c>
+      <c r="C229">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="230" spans="1:3">
+      <c r="A230">
+        <v>2009</v>
+      </c>
+      <c r="B230" t="s">
+        <v>12</v>
+      </c>
+      <c r="C230">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="231" spans="1:3">
+      <c r="A231">
+        <v>2011</v>
+      </c>
+      <c r="B231" t="s">
+        <v>12</v>
+      </c>
+      <c r="C231">
+        <v>14.33333333333333</v>
+      </c>
+    </row>
+    <row r="232" spans="1:3">
+      <c r="A232">
+        <v>2012</v>
+      </c>
+      <c r="B232" t="s">
+        <v>12</v>
+      </c>
+      <c r="C232">
+        <v>13.66666666666667</v>
+      </c>
+    </row>
+    <row r="233" spans="1:3">
+      <c r="A233">
+        <v>2013</v>
+      </c>
+      <c r="B233" t="s">
+        <v>12</v>
+      </c>
+      <c r="C233">
+        <v>13.5</v>
+      </c>
+    </row>
+    <row r="234" spans="1:3">
+      <c r="A234">
+        <v>2014</v>
+      </c>
+      <c r="B234" t="s">
+        <v>12</v>
+      </c>
+      <c r="C234">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="235" spans="1:3">
+      <c r="A235">
+        <v>2015</v>
+      </c>
+      <c r="B235" t="s">
+        <v>12</v>
+      </c>
+      <c r="C235">
+        <v>12.33333333333333</v>
+      </c>
+    </row>
+    <row r="236" spans="1:3">
+      <c r="A236">
+        <v>2016</v>
+      </c>
+      <c r="B236" t="s">
+        <v>12</v>
+      </c>
+      <c r="C236">
+        <v>12.33333333333333</v>
+      </c>
+    </row>
+    <row r="237" spans="1:3">
+      <c r="A237">
+        <v>2017</v>
+      </c>
+      <c r="B237" t="s">
+        <v>12</v>
+      </c>
+      <c r="C237">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="238" spans="1:3">
+      <c r="A238">
+        <v>2018</v>
+      </c>
+      <c r="B238" t="s">
+        <v>12</v>
+      </c>
+      <c r="C238">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="239" spans="1:3">
+      <c r="A239">
+        <v>2019</v>
+      </c>
+      <c r="B239" t="s">
+        <v>12</v>
+      </c>
+      <c r="C239">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="240" spans="1:3">
+      <c r="A240">
+        <v>2020</v>
+      </c>
+      <c r="B240" t="s">
+        <v>12</v>
+      </c>
+      <c r="C240">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="241" spans="1:3">
+      <c r="A241">
+        <v>2021</v>
+      </c>
+      <c r="B241" t="s">
+        <v>12</v>
+      </c>
+      <c r="C241">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="242" spans="1:3">
+      <c r="A242">
+        <v>2022</v>
+      </c>
+      <c r="B242" t="s">
+        <v>12</v>
+      </c>
+      <c r="C242">
+        <v>9.333333333333334</v>
+      </c>
+    </row>
+    <row r="243" spans="1:3">
+      <c r="A243">
+        <v>2023</v>
+      </c>
+      <c r="B243" t="s">
+        <v>12</v>
+      </c>
+      <c r="C243">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="244" spans="1:3">
+      <c r="A244">
+        <v>2024</v>
+      </c>
+      <c r="B244" t="s">
+        <v>12</v>
+      </c>
+      <c r="C244">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="245" spans="1:3">
+      <c r="A245">
+        <v>2025</v>
+      </c>
+      <c r="B245" t="s">
+        <v>12</v>
+      </c>
+      <c r="C245">
         <v>9</v>
       </c>
     </row>

--- a/ratings_mean_clean.xlsx
+++ b/ratings_mean_clean.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="13">
   <si>
     <t>Year</t>
   </si>
@@ -410,7 +410,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C245"/>
+  <dimension ref="A1:C248"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -448,84 +448,84 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="B4" t="s">
         <v>3</v>
       </c>
       <c r="C4">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>2005</v>
+        <v>2003</v>
       </c>
       <c r="B5" t="s">
         <v>3</v>
       </c>
       <c r="C5">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>2006</v>
+        <v>2004</v>
       </c>
       <c r="B6" t="s">
         <v>3</v>
       </c>
       <c r="C6">
-        <v>8.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>2007</v>
+        <v>2005</v>
       </c>
       <c r="B7" t="s">
         <v>3</v>
       </c>
       <c r="C7">
-        <v>7.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>2008</v>
+        <v>2006</v>
       </c>
       <c r="B8" t="s">
         <v>3</v>
       </c>
       <c r="C8">
-        <v>7.333333333333333</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>2009</v>
+        <v>2007</v>
       </c>
       <c r="B9" t="s">
         <v>3</v>
       </c>
       <c r="C9">
-        <v>9</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>2010</v>
+        <v>2008</v>
       </c>
       <c r="B10" t="s">
         <v>3</v>
       </c>
       <c r="C10">
-        <v>7</v>
+        <v>7.333333333333333</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>2011</v>
+        <v>2009</v>
       </c>
       <c r="B11" t="s">
         <v>3</v>
@@ -536,128 +536,128 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="B12" t="s">
         <v>3</v>
       </c>
       <c r="C12">
-        <v>6.5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>2013</v>
+        <v>2011</v>
       </c>
       <c r="B13" t="s">
         <v>3</v>
       </c>
       <c r="C13">
-        <v>6.666666666666667</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="B14" t="s">
         <v>3</v>
       </c>
       <c r="C14">
-        <v>5.666666666666667</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>2015</v>
+        <v>2013</v>
       </c>
       <c r="B15" t="s">
         <v>3</v>
       </c>
       <c r="C15">
-        <v>5</v>
+        <v>6.666666666666667</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="B16" t="s">
         <v>3</v>
       </c>
       <c r="C16">
-        <v>6.333333333333333</v>
+        <v>5.666666666666667</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>2017</v>
+        <v>2015</v>
       </c>
       <c r="B17" t="s">
         <v>3</v>
       </c>
       <c r="C17">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>2018</v>
+        <v>2016</v>
       </c>
       <c r="B18" t="s">
         <v>3</v>
       </c>
       <c r="C18">
-        <v>7</v>
+        <v>6.333333333333333</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>2019</v>
+        <v>2017</v>
       </c>
       <c r="B19" t="s">
         <v>3</v>
       </c>
       <c r="C19">
-        <v>2.666666666666667</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>2020</v>
+        <v>2018</v>
       </c>
       <c r="B20" t="s">
         <v>3</v>
       </c>
       <c r="C20">
-        <v>3.666666666666667</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="B21" t="s">
         <v>3</v>
       </c>
       <c r="C21">
-        <v>4</v>
+        <v>2.666666666666667</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="B22" t="s">
         <v>3</v>
       </c>
       <c r="C22">
-        <v>2.5</v>
+        <v>3.666666666666667</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="B23" t="s">
         <v>3</v>
@@ -668,37 +668,43 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B24" t="s">
         <v>3</v>
       </c>
       <c r="C24">
-        <v>5</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>2000</v>
+        <v>2023</v>
       </c>
       <c r="B25" t="s">
-        <v>4</v>
+        <v>3</v>
+      </c>
+      <c r="C25">
+        <v>3</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>2001</v>
+        <v>2024</v>
       </c>
       <c r="B26" t="s">
+        <v>3</v>
+      </c>
+      <c r="C26">
         <v>4</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>2002</v>
+        <v>2025</v>
       </c>
       <c r="B27" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C27">
         <v>5</v>
@@ -706,213 +712,207 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>2003</v>
+        <v>2000</v>
       </c>
       <c r="B28" t="s">
         <v>4</v>
-      </c>
-      <c r="C28">
-        <v>4.5</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>2004</v>
+        <v>2001</v>
       </c>
       <c r="B29" t="s">
         <v>4</v>
-      </c>
-      <c r="C29">
-        <v>6</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>2005</v>
+        <v>2002</v>
       </c>
       <c r="B30" t="s">
         <v>4</v>
       </c>
       <c r="C30">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>2006</v>
+        <v>2003</v>
       </c>
       <c r="B31" t="s">
         <v>4</v>
       </c>
       <c r="C31">
-        <v>5</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>2007</v>
+        <v>2004</v>
       </c>
       <c r="B32" t="s">
         <v>4</v>
       </c>
       <c r="C32">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>2008</v>
+        <v>2005</v>
       </c>
       <c r="B33" t="s">
         <v>4</v>
       </c>
       <c r="C33">
-        <v>4.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>2009</v>
+        <v>2006</v>
       </c>
       <c r="B34" t="s">
         <v>4</v>
       </c>
       <c r="C34">
-        <v>3.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>2010</v>
+        <v>2007</v>
       </c>
       <c r="B35" t="s">
         <v>4</v>
       </c>
       <c r="C35">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>2011</v>
+        <v>2008</v>
       </c>
       <c r="B36" t="s">
         <v>4</v>
       </c>
       <c r="C36">
-        <v>6</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>2012</v>
+        <v>2009</v>
       </c>
       <c r="B37" t="s">
         <v>4</v>
+      </c>
+      <c r="C37">
+        <v>3.5</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>2013</v>
+        <v>2010</v>
       </c>
       <c r="B38" t="s">
         <v>4</v>
       </c>
       <c r="C38">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>2014</v>
+        <v>2011</v>
       </c>
       <c r="B39" t="s">
         <v>4</v>
       </c>
       <c r="C39">
-        <v>6.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>2015</v>
+        <v>2012</v>
       </c>
       <c r="B40" t="s">
         <v>4</v>
-      </c>
-      <c r="C40">
-        <v>7</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>2016</v>
+        <v>2013</v>
       </c>
       <c r="B41" t="s">
         <v>4</v>
       </c>
       <c r="C41">
-        <v>6.5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>2017</v>
+        <v>2014</v>
       </c>
       <c r="B42" t="s">
         <v>4</v>
       </c>
       <c r="C42">
-        <v>7</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>2018</v>
+        <v>2015</v>
       </c>
       <c r="B43" t="s">
         <v>4</v>
       </c>
       <c r="C43">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>2019</v>
+        <v>2016</v>
       </c>
       <c r="B44" t="s">
         <v>4</v>
       </c>
       <c r="C44">
-        <v>6</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>2020</v>
+        <v>2017</v>
       </c>
       <c r="B45" t="s">
         <v>4</v>
       </c>
       <c r="C45">
-        <v>4.5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>2021</v>
+        <v>2018</v>
       </c>
       <c r="B46" t="s">
         <v>4</v>
       </c>
       <c r="C46">
-        <v>4.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="B47" t="s">
         <v>4</v>
@@ -923,106 +923,106 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>2023</v>
+        <v>2020</v>
       </c>
       <c r="B48" t="s">
         <v>4</v>
       </c>
       <c r="C48">
-        <v>4</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="B49" t="s">
         <v>4</v>
       </c>
       <c r="C49">
-        <v>5</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B50" t="s">
         <v>4</v>
       </c>
       <c r="C50">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>2026</v>
+        <v>2023</v>
       </c>
       <c r="B51" t="s">
         <v>4</v>
       </c>
       <c r="C51">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>2000</v>
+        <v>2024</v>
       </c>
       <c r="B52" t="s">
+        <v>4</v>
+      </c>
+      <c r="C52">
         <v>5</v>
-      </c>
-      <c r="C52">
-        <v>12</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>2001</v>
+        <v>2025</v>
       </c>
       <c r="B53" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C53">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>2002</v>
+        <v>2026</v>
       </c>
       <c r="B54" t="s">
+        <v>4</v>
+      </c>
+      <c r="C54">
         <v>5</v>
-      </c>
-      <c r="C54">
-        <v>11</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>2003</v>
+        <v>2000</v>
       </c>
       <c r="B55" t="s">
         <v>5</v>
       </c>
       <c r="C55">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>2004</v>
+        <v>2001</v>
       </c>
       <c r="B56" t="s">
         <v>5</v>
       </c>
       <c r="C56">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>2005</v>
+        <v>2002</v>
       </c>
       <c r="B57" t="s">
         <v>5</v>
@@ -1033,7 +1033,7 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>2007</v>
+        <v>2003</v>
       </c>
       <c r="B58" t="s">
         <v>5</v>
@@ -1044,7 +1044,7 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>2008</v>
+        <v>2004</v>
       </c>
       <c r="B59" t="s">
         <v>5</v>
@@ -1055,7 +1055,7 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>2009</v>
+        <v>2005</v>
       </c>
       <c r="B60" t="s">
         <v>5</v>
@@ -1066,205 +1066,205 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>2011</v>
+        <v>2007</v>
       </c>
       <c r="B61" t="s">
         <v>5</v>
       </c>
       <c r="C61">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>2012</v>
+        <v>2008</v>
       </c>
       <c r="B62" t="s">
         <v>5</v>
       </c>
       <c r="C62">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>2013</v>
+        <v>2009</v>
       </c>
       <c r="B63" t="s">
         <v>5</v>
       </c>
       <c r="C63">
-        <v>5.666666666666667</v>
+        <v>11</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>2014</v>
+        <v>2011</v>
       </c>
       <c r="B64" t="s">
         <v>5</v>
       </c>
       <c r="C64">
-        <v>5.5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>2015</v>
+        <v>2012</v>
       </c>
       <c r="B65" t="s">
         <v>5</v>
       </c>
       <c r="C65">
-        <v>6.333333333333333</v>
+        <v>7</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>2016</v>
+        <v>2013</v>
       </c>
       <c r="B66" t="s">
         <v>5</v>
       </c>
       <c r="C66">
-        <v>6.333333333333333</v>
+        <v>5.666666666666667</v>
       </c>
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>2017</v>
+        <v>2014</v>
       </c>
       <c r="B67" t="s">
         <v>5</v>
       </c>
       <c r="C67">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>2018</v>
+        <v>2015</v>
       </c>
       <c r="B68" t="s">
         <v>5</v>
       </c>
       <c r="C68">
-        <v>6.666666666666667</v>
+        <v>6.333333333333333</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>2019</v>
+        <v>2016</v>
       </c>
       <c r="B69" t="s">
         <v>5</v>
       </c>
       <c r="C69">
-        <v>7.333333333333333</v>
+        <v>6.333333333333333</v>
       </c>
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>2020</v>
+        <v>2017</v>
       </c>
       <c r="B70" t="s">
         <v>5</v>
       </c>
       <c r="C70">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>2021</v>
+        <v>2018</v>
       </c>
       <c r="B71" t="s">
         <v>5</v>
       </c>
       <c r="C71">
-        <v>7.5</v>
+        <v>6.666666666666667</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="B72" t="s">
         <v>5</v>
       </c>
       <c r="C72">
-        <v>7.5</v>
+        <v>7.333333333333333</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>2023</v>
+        <v>2020</v>
       </c>
       <c r="B73" t="s">
         <v>5</v>
       </c>
       <c r="C73">
-        <v>6</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="B74" t="s">
         <v>5</v>
       </c>
       <c r="C74">
-        <v>6</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B75" t="s">
         <v>5</v>
       </c>
       <c r="C75">
-        <v>6.333333333333333</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>2000</v>
+        <v>2023</v>
       </c>
       <c r="B76" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C76">
-        <v>21</v>
+        <v>6</v>
       </c>
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>2001</v>
+        <v>2024</v>
       </c>
       <c r="B77" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C77">
-        <v>21</v>
+        <v>6</v>
       </c>
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>2002</v>
+        <v>2025</v>
       </c>
       <c r="B78" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C78">
-        <v>21</v>
+        <v>6.333333333333333</v>
       </c>
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>2003</v>
+        <v>2000</v>
       </c>
       <c r="B79" t="s">
         <v>6</v>
@@ -1275,7 +1275,7 @@
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>2004</v>
+        <v>2001</v>
       </c>
       <c r="B80" t="s">
         <v>6</v>
@@ -1286,7 +1286,7 @@
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>2005</v>
+        <v>2002</v>
       </c>
       <c r="B81" t="s">
         <v>6</v>
@@ -1297,7 +1297,7 @@
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>2006</v>
+        <v>2003</v>
       </c>
       <c r="B82" t="s">
         <v>6</v>
@@ -1308,7 +1308,7 @@
     </row>
     <row r="83" spans="1:3">
       <c r="A83">
-        <v>2007</v>
+        <v>2004</v>
       </c>
       <c r="B83" t="s">
         <v>6</v>
@@ -1319,7 +1319,7 @@
     </row>
     <row r="84" spans="1:3">
       <c r="A84">
-        <v>2008</v>
+        <v>2005</v>
       </c>
       <c r="B84" t="s">
         <v>6</v>
@@ -1330,7 +1330,7 @@
     </row>
     <row r="85" spans="1:3">
       <c r="A85">
-        <v>2009</v>
+        <v>2006</v>
       </c>
       <c r="B85" t="s">
         <v>6</v>
@@ -1341,7 +1341,7 @@
     </row>
     <row r="86" spans="1:3">
       <c r="A86">
-        <v>2010</v>
+        <v>2007</v>
       </c>
       <c r="B86" t="s">
         <v>6</v>
@@ -1352,7 +1352,7 @@
     </row>
     <row r="87" spans="1:3">
       <c r="A87">
-        <v>2011</v>
+        <v>2008</v>
       </c>
       <c r="B87" t="s">
         <v>6</v>
@@ -1363,73 +1363,73 @@
     </row>
     <row r="88" spans="1:3">
       <c r="A88">
-        <v>2012</v>
+        <v>2009</v>
       </c>
       <c r="B88" t="s">
         <v>6</v>
       </c>
       <c r="C88">
-        <v>20.33333333333333</v>
+        <v>21</v>
       </c>
     </row>
     <row r="89" spans="1:3">
       <c r="A89">
-        <v>2013</v>
+        <v>2010</v>
       </c>
       <c r="B89" t="s">
         <v>6</v>
       </c>
       <c r="C89">
-        <v>19.5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="90" spans="1:3">
       <c r="A90">
-        <v>2014</v>
+        <v>2011</v>
       </c>
       <c r="B90" t="s">
         <v>6</v>
       </c>
       <c r="C90">
-        <v>19.5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="91" spans="1:3">
       <c r="A91">
-        <v>2015</v>
+        <v>2012</v>
       </c>
       <c r="B91" t="s">
         <v>6</v>
       </c>
       <c r="C91">
-        <v>19</v>
+        <v>20.33333333333333</v>
       </c>
     </row>
     <row r="92" spans="1:3">
       <c r="A92">
-        <v>2016</v>
+        <v>2013</v>
       </c>
       <c r="B92" t="s">
         <v>6</v>
       </c>
       <c r="C92">
-        <v>19</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="93" spans="1:3">
       <c r="A93">
-        <v>2017</v>
+        <v>2014</v>
       </c>
       <c r="B93" t="s">
         <v>6</v>
       </c>
       <c r="C93">
-        <v>19</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="94" spans="1:3">
       <c r="A94">
-        <v>2018</v>
+        <v>2015</v>
       </c>
       <c r="B94" t="s">
         <v>6</v>
@@ -1440,7 +1440,7 @@
     </row>
     <row r="95" spans="1:3">
       <c r="A95">
-        <v>2019</v>
+        <v>2016</v>
       </c>
       <c r="B95" t="s">
         <v>6</v>
@@ -1451,7 +1451,7 @@
     </row>
     <row r="96" spans="1:3">
       <c r="A96">
-        <v>2020</v>
+        <v>2017</v>
       </c>
       <c r="B96" t="s">
         <v>6</v>
@@ -1462,7 +1462,7 @@
     </row>
     <row r="97" spans="1:3">
       <c r="A97">
-        <v>2021</v>
+        <v>2018</v>
       </c>
       <c r="B97" t="s">
         <v>6</v>
@@ -1473,7 +1473,7 @@
     </row>
     <row r="98" spans="1:3">
       <c r="A98">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="B98" t="s">
         <v>6</v>
@@ -1484,84 +1484,84 @@
     </row>
     <row r="99" spans="1:3">
       <c r="A99">
-        <v>2023</v>
+        <v>2020</v>
       </c>
       <c r="B99" t="s">
         <v>6</v>
       </c>
       <c r="C99">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="100" spans="1:3">
       <c r="A100">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="B100" t="s">
         <v>6</v>
       </c>
       <c r="C100">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="101" spans="1:3">
       <c r="A101">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B101" t="s">
         <v>6</v>
       </c>
       <c r="C101">
-        <v>17.33333333333333</v>
+        <v>19</v>
       </c>
     </row>
     <row r="102" spans="1:3">
       <c r="A102">
-        <v>2000</v>
+        <v>2023</v>
       </c>
       <c r="B102" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C102">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="103" spans="1:3">
       <c r="A103">
-        <v>2001</v>
+        <v>2024</v>
       </c>
       <c r="B103" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C103">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="104" spans="1:3">
       <c r="A104">
-        <v>2002</v>
+        <v>2025</v>
       </c>
       <c r="B104" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C104">
-        <v>16</v>
+        <v>17.33333333333333</v>
       </c>
     </row>
     <row r="105" spans="1:3">
       <c r="A105">
-        <v>2003</v>
+        <v>2000</v>
       </c>
       <c r="B105" t="s">
         <v>7</v>
       </c>
       <c r="C105">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="106" spans="1:3">
       <c r="A106">
-        <v>2004</v>
+        <v>2001</v>
       </c>
       <c r="B106" t="s">
         <v>7</v>
@@ -1572,7 +1572,7 @@
     </row>
     <row r="107" spans="1:3">
       <c r="A107">
-        <v>2005</v>
+        <v>2002</v>
       </c>
       <c r="B107" t="s">
         <v>7</v>
@@ -1583,18 +1583,18 @@
     </row>
     <row r="108" spans="1:3">
       <c r="A108">
-        <v>2007</v>
+        <v>2003</v>
       </c>
       <c r="B108" t="s">
         <v>7</v>
       </c>
       <c r="C108">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="109" spans="1:3">
       <c r="A109">
-        <v>2008</v>
+        <v>2004</v>
       </c>
       <c r="B109" t="s">
         <v>7</v>
@@ -1605,359 +1605,359 @@
     </row>
     <row r="110" spans="1:3">
       <c r="A110">
-        <v>2009</v>
+        <v>2005</v>
       </c>
       <c r="B110" t="s">
         <v>7</v>
       </c>
       <c r="C110">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="111" spans="1:3">
       <c r="A111">
-        <v>2010</v>
+        <v>2007</v>
       </c>
       <c r="B111" t="s">
         <v>7</v>
       </c>
       <c r="C111">
-        <v>11.33333333333333</v>
+        <v>16</v>
       </c>
     </row>
     <row r="112" spans="1:3">
       <c r="A112">
-        <v>2011</v>
+        <v>2008</v>
       </c>
       <c r="B112" t="s">
         <v>7</v>
       </c>
       <c r="C112">
-        <v>4</v>
+        <v>16</v>
       </c>
     </row>
     <row r="113" spans="1:3">
       <c r="A113">
-        <v>2012</v>
+        <v>2009</v>
       </c>
       <c r="B113" t="s">
         <v>7</v>
       </c>
       <c r="C113">
-        <v>6</v>
+        <v>15</v>
       </c>
     </row>
     <row r="114" spans="1:3">
       <c r="A114">
-        <v>2013</v>
+        <v>2010</v>
       </c>
       <c r="B114" t="s">
         <v>7</v>
       </c>
       <c r="C114">
-        <v>4.5</v>
+        <v>11.33333333333333</v>
       </c>
     </row>
     <row r="115" spans="1:3">
       <c r="A115">
-        <v>2014</v>
+        <v>2011</v>
       </c>
       <c r="B115" t="s">
         <v>7</v>
       </c>
       <c r="C115">
-        <v>6.333333333333333</v>
+        <v>4</v>
       </c>
     </row>
     <row r="116" spans="1:3">
       <c r="A116">
-        <v>2015</v>
+        <v>2012</v>
       </c>
       <c r="B116" t="s">
         <v>7</v>
       </c>
       <c r="C116">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="117" spans="1:3">
       <c r="A117">
-        <v>2016</v>
+        <v>2013</v>
       </c>
       <c r="B117" t="s">
         <v>7</v>
       </c>
       <c r="C117">
-        <v>6</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="118" spans="1:3">
       <c r="A118">
-        <v>2017</v>
+        <v>2014</v>
       </c>
       <c r="B118" t="s">
         <v>7</v>
       </c>
       <c r="C118">
-        <v>5.333333333333333</v>
+        <v>6.333333333333333</v>
       </c>
     </row>
     <row r="119" spans="1:3">
       <c r="A119">
-        <v>2018</v>
+        <v>2015</v>
       </c>
       <c r="B119" t="s">
         <v>7</v>
       </c>
       <c r="C119">
-        <v>7.666666666666667</v>
+        <v>4</v>
       </c>
     </row>
     <row r="120" spans="1:3">
       <c r="A120">
-        <v>2019</v>
+        <v>2016</v>
       </c>
       <c r="B120" t="s">
         <v>7</v>
       </c>
       <c r="C120">
-        <v>8.666666666666666</v>
+        <v>6</v>
       </c>
     </row>
     <row r="121" spans="1:3">
       <c r="A121">
-        <v>2020</v>
+        <v>2017</v>
       </c>
       <c r="B121" t="s">
         <v>7</v>
       </c>
       <c r="C121">
-        <v>10</v>
+        <v>5.333333333333333</v>
       </c>
     </row>
     <row r="122" spans="1:3">
       <c r="A122">
-        <v>2021</v>
+        <v>2018</v>
       </c>
       <c r="B122" t="s">
         <v>7</v>
       </c>
       <c r="C122">
-        <v>9.5</v>
+        <v>7.666666666666667</v>
       </c>
     </row>
     <row r="123" spans="1:3">
       <c r="A123">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="B123" t="s">
         <v>7</v>
       </c>
       <c r="C123">
-        <v>9.5</v>
+        <v>8.666666666666666</v>
       </c>
     </row>
     <row r="124" spans="1:3">
       <c r="A124">
-        <v>2023</v>
+        <v>2020</v>
       </c>
       <c r="B124" t="s">
         <v>7</v>
       </c>
       <c r="C124">
-        <v>11.66666666666667</v>
+        <v>10</v>
       </c>
     </row>
     <row r="125" spans="1:3">
       <c r="A125">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="B125" t="s">
         <v>7</v>
       </c>
       <c r="C125">
-        <v>11.5</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="126" spans="1:3">
       <c r="A126">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B126" t="s">
         <v>7</v>
       </c>
       <c r="C126">
-        <v>12.33333333333333</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="127" spans="1:3">
       <c r="A127">
-        <v>2000</v>
+        <v>2023</v>
       </c>
       <c r="B127" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C127">
-        <v>20</v>
+        <v>11.66666666666667</v>
       </c>
     </row>
     <row r="128" spans="1:3">
       <c r="A128">
-        <v>2001</v>
+        <v>2024</v>
       </c>
       <c r="B128" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C128">
-        <v>19</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="129" spans="1:3">
       <c r="A129">
-        <v>2002</v>
+        <v>2025</v>
       </c>
       <c r="B129" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C129">
-        <v>19</v>
+        <v>12.33333333333333</v>
       </c>
     </row>
     <row r="130" spans="1:3">
       <c r="A130">
-        <v>2004</v>
+        <v>2000</v>
       </c>
       <c r="B130" t="s">
         <v>8</v>
       </c>
       <c r="C130">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="131" spans="1:3">
       <c r="A131">
-        <v>2005</v>
+        <v>2001</v>
       </c>
       <c r="B131" t="s">
         <v>8</v>
       </c>
       <c r="C131">
-        <v>18.5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="132" spans="1:3">
       <c r="A132">
-        <v>2006</v>
+        <v>2002</v>
       </c>
       <c r="B132" t="s">
         <v>8</v>
       </c>
       <c r="C132">
-        <v>19.5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="133" spans="1:3">
       <c r="A133">
-        <v>2007</v>
+        <v>2004</v>
       </c>
       <c r="B133" t="s">
         <v>8</v>
       </c>
       <c r="C133">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="134" spans="1:3">
       <c r="A134">
-        <v>2010</v>
+        <v>2005</v>
       </c>
       <c r="B134" t="s">
         <v>8</v>
       </c>
       <c r="C134">
-        <v>19</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="135" spans="1:3">
       <c r="A135">
-        <v>2011</v>
+        <v>2006</v>
       </c>
       <c r="B135" t="s">
         <v>8</v>
       </c>
       <c r="C135">
-        <v>18.33333333333333</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="136" spans="1:3">
       <c r="A136">
-        <v>2012</v>
+        <v>2007</v>
       </c>
       <c r="B136" t="s">
         <v>8</v>
       </c>
       <c r="C136">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="137" spans="1:3">
       <c r="A137">
-        <v>2013</v>
+        <v>2010</v>
       </c>
       <c r="B137" t="s">
         <v>8</v>
       </c>
       <c r="C137">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="138" spans="1:3">
       <c r="A138">
-        <v>2014</v>
+        <v>2011</v>
       </c>
       <c r="B138" t="s">
         <v>8</v>
       </c>
       <c r="C138">
-        <v>17</v>
+        <v>18.33333333333333</v>
       </c>
     </row>
     <row r="139" spans="1:3">
       <c r="A139">
-        <v>2015</v>
+        <v>2012</v>
       </c>
       <c r="B139" t="s">
         <v>8</v>
       </c>
       <c r="C139">
-        <v>16.5</v>
+        <v>17</v>
       </c>
     </row>
     <row r="140" spans="1:3">
       <c r="A140">
-        <v>2016</v>
+        <v>2013</v>
       </c>
       <c r="B140" t="s">
         <v>8</v>
       </c>
       <c r="C140">
-        <v>16.5</v>
+        <v>17</v>
       </c>
     </row>
     <row r="141" spans="1:3">
       <c r="A141">
-        <v>2017</v>
+        <v>2014</v>
       </c>
       <c r="B141" t="s">
         <v>8</v>
       </c>
       <c r="C141">
-        <v>16.5</v>
+        <v>17</v>
       </c>
     </row>
     <row r="142" spans="1:3">
       <c r="A142">
-        <v>2018</v>
+        <v>2015</v>
       </c>
       <c r="B142" t="s">
         <v>8</v>
@@ -1968,7 +1968,7 @@
     </row>
     <row r="143" spans="1:3">
       <c r="A143">
-        <v>2019</v>
+        <v>2016</v>
       </c>
       <c r="B143" t="s">
         <v>8</v>
@@ -1979,7 +1979,7 @@
     </row>
     <row r="144" spans="1:3">
       <c r="A144">
-        <v>2020</v>
+        <v>2017</v>
       </c>
       <c r="B144" t="s">
         <v>8</v>
@@ -1990,7 +1990,7 @@
     </row>
     <row r="145" spans="1:3">
       <c r="A145">
-        <v>2021</v>
+        <v>2018</v>
       </c>
       <c r="B145" t="s">
         <v>8</v>
@@ -2001,18 +2001,18 @@
     </row>
     <row r="146" spans="1:3">
       <c r="A146">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="B146" t="s">
         <v>8</v>
       </c>
       <c r="C146">
-        <v>16</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="147" spans="1:3">
       <c r="A147">
-        <v>2023</v>
+        <v>2020</v>
       </c>
       <c r="B147" t="s">
         <v>8</v>
@@ -2023,64 +2023,73 @@
     </row>
     <row r="148" spans="1:3">
       <c r="A148">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="B148" t="s">
         <v>8</v>
       </c>
       <c r="C148">
-        <v>16</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="149" spans="1:3">
       <c r="A149">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B149" t="s">
         <v>8</v>
       </c>
       <c r="C149">
-        <v>16.5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="150" spans="1:3">
       <c r="A150">
-        <v>2000</v>
+        <v>2023</v>
       </c>
       <c r="B150" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C150">
-        <v>21</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="151" spans="1:3">
       <c r="A151">
-        <v>2001</v>
+        <v>2024</v>
       </c>
       <c r="B151" t="s">
-        <v>9</v>
+        <v>8</v>
+      </c>
+      <c r="C151">
+        <v>16</v>
       </c>
     </row>
     <row r="152" spans="1:3">
       <c r="A152">
-        <v>2002</v>
+        <v>2025</v>
       </c>
       <c r="B152" t="s">
-        <v>9</v>
+        <v>8</v>
+      </c>
+      <c r="C152">
+        <v>16.5</v>
       </c>
     </row>
     <row r="153" spans="1:3">
       <c r="A153">
-        <v>2003</v>
+        <v>2000</v>
       </c>
       <c r="B153" t="s">
         <v>9</v>
+      </c>
+      <c r="C153">
+        <v>21</v>
       </c>
     </row>
     <row r="154" spans="1:3">
       <c r="A154">
-        <v>2004</v>
+        <v>2001</v>
       </c>
       <c r="B154" t="s">
         <v>9</v>
@@ -2088,7 +2097,7 @@
     </row>
     <row r="155" spans="1:3">
       <c r="A155">
-        <v>2005</v>
+        <v>2002</v>
       </c>
       <c r="B155" t="s">
         <v>9</v>
@@ -2096,7 +2105,7 @@
     </row>
     <row r="156" spans="1:3">
       <c r="A156">
-        <v>2006</v>
+        <v>2003</v>
       </c>
       <c r="B156" t="s">
         <v>9</v>
@@ -2104,7 +2113,7 @@
     </row>
     <row r="157" spans="1:3">
       <c r="A157">
-        <v>2007</v>
+        <v>2004</v>
       </c>
       <c r="B157" t="s">
         <v>9</v>
@@ -2112,7 +2121,7 @@
     </row>
     <row r="158" spans="1:3">
       <c r="A158">
-        <v>2008</v>
+        <v>2005</v>
       </c>
       <c r="B158" t="s">
         <v>9</v>
@@ -2120,7 +2129,7 @@
     </row>
     <row r="159" spans="1:3">
       <c r="A159">
-        <v>2009</v>
+        <v>2006</v>
       </c>
       <c r="B159" t="s">
         <v>9</v>
@@ -2128,7 +2137,7 @@
     </row>
     <row r="160" spans="1:3">
       <c r="A160">
-        <v>2010</v>
+        <v>2007</v>
       </c>
       <c r="B160" t="s">
         <v>9</v>
@@ -2136,139 +2145,130 @@
     </row>
     <row r="161" spans="1:3">
       <c r="A161">
-        <v>2011</v>
+        <v>2008</v>
       </c>
       <c r="B161" t="s">
         <v>9</v>
-      </c>
-      <c r="C161">
-        <v>21</v>
       </c>
     </row>
     <row r="162" spans="1:3">
       <c r="A162">
-        <v>2012</v>
+        <v>2009</v>
       </c>
       <c r="B162" t="s">
         <v>9</v>
-      </c>
-      <c r="C162">
-        <v>21</v>
       </c>
     </row>
     <row r="163" spans="1:3">
       <c r="A163">
-        <v>2013</v>
+        <v>2010</v>
       </c>
       <c r="B163" t="s">
         <v>9</v>
-      </c>
-      <c r="C163">
-        <v>20.11111111111111</v>
       </c>
     </row>
     <row r="164" spans="1:3">
       <c r="A164">
-        <v>2014</v>
+        <v>2011</v>
       </c>
       <c r="B164" t="s">
         <v>9</v>
       </c>
       <c r="C164">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="165" spans="1:3">
       <c r="A165">
-        <v>2015</v>
+        <v>2012</v>
       </c>
       <c r="B165" t="s">
         <v>9</v>
       </c>
       <c r="C165">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="166" spans="1:3">
       <c r="A166">
-        <v>2016</v>
+        <v>2013</v>
       </c>
       <c r="B166" t="s">
         <v>9</v>
       </c>
       <c r="C166">
-        <v>19.25</v>
+        <v>20.11111111111111</v>
       </c>
     </row>
     <row r="167" spans="1:3">
       <c r="A167">
-        <v>2017</v>
+        <v>2014</v>
       </c>
       <c r="B167" t="s">
         <v>9</v>
       </c>
       <c r="C167">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="168" spans="1:3">
       <c r="A168">
-        <v>2018</v>
+        <v>2015</v>
       </c>
       <c r="B168" t="s">
         <v>9</v>
       </c>
       <c r="C168">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="169" spans="1:3">
       <c r="A169">
-        <v>2019</v>
+        <v>2016</v>
       </c>
       <c r="B169" t="s">
         <v>9</v>
       </c>
       <c r="C169">
-        <v>19</v>
+        <v>19.25</v>
       </c>
     </row>
     <row r="170" spans="1:3">
       <c r="A170">
-        <v>2020</v>
+        <v>2017</v>
       </c>
       <c r="B170" t="s">
         <v>9</v>
       </c>
       <c r="C170">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="171" spans="1:3">
       <c r="A171">
-        <v>2021</v>
+        <v>2018</v>
       </c>
       <c r="B171" t="s">
         <v>9</v>
       </c>
       <c r="C171">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="172" spans="1:3">
       <c r="A172">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="B172" t="s">
         <v>9</v>
       </c>
       <c r="C172">
-        <v>15.6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="173" spans="1:3">
       <c r="A173">
-        <v>2023</v>
+        <v>2020</v>
       </c>
       <c r="B173" t="s">
         <v>9</v>
@@ -2279,7 +2279,7 @@
     </row>
     <row r="174" spans="1:3">
       <c r="A174">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="B174" t="s">
         <v>9</v>
@@ -2290,45 +2290,51 @@
     </row>
     <row r="175" spans="1:3">
       <c r="A175">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B175" t="s">
         <v>9</v>
       </c>
       <c r="C175">
-        <v>18</v>
+        <v>15.6</v>
       </c>
     </row>
     <row r="176" spans="1:3">
       <c r="A176">
-        <v>2000</v>
+        <v>2023</v>
       </c>
       <c r="B176" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C176">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="177" spans="1:3">
       <c r="A177">
-        <v>2001</v>
+        <v>2024</v>
       </c>
       <c r="B177" t="s">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="C177">
+        <v>18</v>
       </c>
     </row>
     <row r="178" spans="1:3">
       <c r="A178">
-        <v>2002</v>
+        <v>2025</v>
       </c>
       <c r="B178" t="s">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="C178">
+        <v>18</v>
       </c>
     </row>
     <row r="179" spans="1:3">
       <c r="A179">
-        <v>2003</v>
+        <v>2000</v>
       </c>
       <c r="B179" t="s">
         <v>10</v>
@@ -2339,7 +2345,7 @@
     </row>
     <row r="180" spans="1:3">
       <c r="A180">
-        <v>2004</v>
+        <v>2001</v>
       </c>
       <c r="B180" t="s">
         <v>10</v>
@@ -2347,7 +2353,7 @@
     </row>
     <row r="181" spans="1:3">
       <c r="A181">
-        <v>2005</v>
+        <v>2002</v>
       </c>
       <c r="B181" t="s">
         <v>10</v>
@@ -2355,15 +2361,18 @@
     </row>
     <row r="182" spans="1:3">
       <c r="A182">
-        <v>2006</v>
+        <v>2003</v>
       </c>
       <c r="B182" t="s">
         <v>10</v>
+      </c>
+      <c r="C182">
+        <v>21</v>
       </c>
     </row>
     <row r="183" spans="1:3">
       <c r="A183">
-        <v>2007</v>
+        <v>2004</v>
       </c>
       <c r="B183" t="s">
         <v>10</v>
@@ -2371,7 +2380,7 @@
     </row>
     <row r="184" spans="1:3">
       <c r="A184">
-        <v>2008</v>
+        <v>2005</v>
       </c>
       <c r="B184" t="s">
         <v>10</v>
@@ -2379,7 +2388,7 @@
     </row>
     <row r="185" spans="1:3">
       <c r="A185">
-        <v>2009</v>
+        <v>2006</v>
       </c>
       <c r="B185" t="s">
         <v>10</v>
@@ -2387,7 +2396,7 @@
     </row>
     <row r="186" spans="1:3">
       <c r="A186">
-        <v>2010</v>
+        <v>2007</v>
       </c>
       <c r="B186" t="s">
         <v>10</v>
@@ -2395,40 +2404,31 @@
     </row>
     <row r="187" spans="1:3">
       <c r="A187">
-        <v>2011</v>
+        <v>2008</v>
       </c>
       <c r="B187" t="s">
         <v>10</v>
-      </c>
-      <c r="C187">
-        <v>21</v>
       </c>
     </row>
     <row r="188" spans="1:3">
       <c r="A188">
-        <v>2012</v>
+        <v>2009</v>
       </c>
       <c r="B188" t="s">
         <v>10</v>
-      </c>
-      <c r="C188">
-        <v>21</v>
       </c>
     </row>
     <row r="189" spans="1:3">
       <c r="A189">
-        <v>2013</v>
+        <v>2010</v>
       </c>
       <c r="B189" t="s">
         <v>10</v>
-      </c>
-      <c r="C189">
-        <v>21</v>
       </c>
     </row>
     <row r="190" spans="1:3">
       <c r="A190">
-        <v>2014</v>
+        <v>2011</v>
       </c>
       <c r="B190" t="s">
         <v>10</v>
@@ -2439,7 +2439,7 @@
     </row>
     <row r="191" spans="1:3">
       <c r="A191">
-        <v>2015</v>
+        <v>2012</v>
       </c>
       <c r="B191" t="s">
         <v>10</v>
@@ -2450,7 +2450,7 @@
     </row>
     <row r="192" spans="1:3">
       <c r="A192">
-        <v>2016</v>
+        <v>2013</v>
       </c>
       <c r="B192" t="s">
         <v>10</v>
@@ -2461,7 +2461,7 @@
     </row>
     <row r="193" spans="1:3">
       <c r="A193">
-        <v>2017</v>
+        <v>2014</v>
       </c>
       <c r="B193" t="s">
         <v>10</v>
@@ -2472,7 +2472,7 @@
     </row>
     <row r="194" spans="1:3">
       <c r="A194">
-        <v>2018</v>
+        <v>2015</v>
       </c>
       <c r="B194" t="s">
         <v>10</v>
@@ -2483,7 +2483,7 @@
     </row>
     <row r="195" spans="1:3">
       <c r="A195">
-        <v>2019</v>
+        <v>2016</v>
       </c>
       <c r="B195" t="s">
         <v>10</v>
@@ -2494,7 +2494,7 @@
     </row>
     <row r="196" spans="1:3">
       <c r="A196">
-        <v>2020</v>
+        <v>2017</v>
       </c>
       <c r="B196" t="s">
         <v>10</v>
@@ -2505,15 +2505,18 @@
     </row>
     <row r="197" spans="1:3">
       <c r="A197">
-        <v>2021</v>
+        <v>2018</v>
       </c>
       <c r="B197" t="s">
         <v>10</v>
+      </c>
+      <c r="C197">
+        <v>21</v>
       </c>
     </row>
     <row r="198" spans="1:3">
       <c r="A198">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="B198" t="s">
         <v>10</v>
@@ -2524,75 +2527,81 @@
     </row>
     <row r="199" spans="1:3">
       <c r="A199">
-        <v>2023</v>
+        <v>2020</v>
       </c>
       <c r="B199" t="s">
         <v>10</v>
       </c>
       <c r="C199">
-        <v>20.5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="200" spans="1:3">
       <c r="A200">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="B200" t="s">
         <v>10</v>
-      </c>
-      <c r="C200">
-        <v>20</v>
       </c>
     </row>
     <row r="201" spans="1:3">
       <c r="A201">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B201" t="s">
         <v>10</v>
       </c>
       <c r="C201">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="202" spans="1:3">
       <c r="A202">
-        <v>2001</v>
+        <v>2023</v>
       </c>
       <c r="B202" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C202">
-        <v>8</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="203" spans="1:3">
       <c r="A203">
-        <v>2002</v>
+        <v>2024</v>
       </c>
       <c r="B203" t="s">
-        <v>11</v>
+        <v>10</v>
+      </c>
+      <c r="C203">
+        <v>20</v>
       </c>
     </row>
     <row r="204" spans="1:3">
       <c r="A204">
-        <v>2005</v>
+        <v>2025</v>
       </c>
       <c r="B204" t="s">
-        <v>11</v>
+        <v>10</v>
+      </c>
+      <c r="C204">
+        <v>20</v>
       </c>
     </row>
     <row r="205" spans="1:3">
       <c r="A205">
-        <v>2006</v>
+        <v>2001</v>
       </c>
       <c r="B205" t="s">
         <v>11</v>
       </c>
+      <c r="C205">
+        <v>8</v>
+      </c>
     </row>
     <row r="206" spans="1:3">
       <c r="A206">
-        <v>2007</v>
+        <v>2002</v>
       </c>
       <c r="B206" t="s">
         <v>11</v>
@@ -2600,7 +2609,7 @@
     </row>
     <row r="207" spans="1:3">
       <c r="A207">
-        <v>2008</v>
+        <v>2005</v>
       </c>
       <c r="B207" t="s">
         <v>11</v>
@@ -2608,18 +2617,15 @@
     </row>
     <row r="208" spans="1:3">
       <c r="A208">
-        <v>2010</v>
+        <v>2006</v>
       </c>
       <c r="B208" t="s">
         <v>11</v>
       </c>
-      <c r="C208">
-        <v>10</v>
-      </c>
     </row>
     <row r="209" spans="1:3">
       <c r="A209">
-        <v>2011</v>
+        <v>2007</v>
       </c>
       <c r="B209" t="s">
         <v>11</v>
@@ -2627,86 +2633,83 @@
     </row>
     <row r="210" spans="1:3">
       <c r="A210">
-        <v>2012</v>
+        <v>2008</v>
       </c>
       <c r="B210" t="s">
         <v>11</v>
       </c>
-      <c r="C210">
-        <v>10</v>
-      </c>
     </row>
     <row r="211" spans="1:3">
       <c r="A211">
-        <v>2014</v>
+        <v>2010</v>
       </c>
       <c r="B211" t="s">
         <v>11</v>
       </c>
+      <c r="C211">
+        <v>10</v>
+      </c>
     </row>
     <row r="212" spans="1:3">
       <c r="A212">
-        <v>2016</v>
+        <v>2011</v>
       </c>
       <c r="B212" t="s">
         <v>11</v>
       </c>
-      <c r="C212">
-        <v>11</v>
-      </c>
     </row>
     <row r="213" spans="1:3">
       <c r="A213">
-        <v>2017</v>
+        <v>2012</v>
       </c>
       <c r="B213" t="s">
         <v>11</v>
       </c>
+      <c r="C213">
+        <v>10</v>
+      </c>
     </row>
     <row r="214" spans="1:3">
       <c r="A214">
-        <v>2018</v>
+        <v>2014</v>
       </c>
       <c r="B214" t="s">
         <v>11</v>
       </c>
-      <c r="C214">
-        <v>10.5</v>
-      </c>
     </row>
     <row r="215" spans="1:3">
       <c r="A215">
-        <v>2019</v>
+        <v>2016</v>
       </c>
       <c r="B215" t="s">
         <v>11</v>
       </c>
       <c r="C215">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="216" spans="1:3">
       <c r="A216">
-        <v>2020</v>
+        <v>2017</v>
       </c>
       <c r="B216" t="s">
         <v>11</v>
       </c>
-      <c r="C216">
-        <v>10</v>
-      </c>
     </row>
     <row r="217" spans="1:3">
       <c r="A217">
-        <v>2021</v>
+        <v>2018</v>
       </c>
       <c r="B217" t="s">
         <v>11</v>
       </c>
+      <c r="C217">
+        <v>10.5</v>
+      </c>
     </row>
     <row r="218" spans="1:3">
       <c r="A218">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="B218" t="s">
         <v>11</v>
@@ -2717,265 +2720,262 @@
     </row>
     <row r="219" spans="1:3">
       <c r="A219">
-        <v>2023</v>
+        <v>2020</v>
       </c>
       <c r="B219" t="s">
         <v>11</v>
       </c>
+      <c r="C219">
+        <v>10</v>
+      </c>
     </row>
     <row r="220" spans="1:3">
       <c r="A220">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="B220" t="s">
         <v>11</v>
       </c>
-      <c r="C220">
-        <v>9</v>
-      </c>
     </row>
     <row r="221" spans="1:3">
       <c r="A221">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B221" t="s">
         <v>11</v>
       </c>
       <c r="C221">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="222" spans="1:3">
       <c r="A222">
-        <v>2000</v>
+        <v>2023</v>
       </c>
       <c r="B222" t="s">
-        <v>12</v>
-      </c>
-      <c r="C222">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="223" spans="1:3">
       <c r="A223">
-        <v>2001</v>
+        <v>2024</v>
       </c>
       <c r="B223" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C223">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="224" spans="1:3">
       <c r="A224">
-        <v>2002</v>
+        <v>2025</v>
       </c>
       <c r="B224" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C224">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="225" spans="1:3">
       <c r="A225">
-        <v>2003</v>
+        <v>2000</v>
       </c>
       <c r="B225" t="s">
         <v>12</v>
       </c>
       <c r="C225">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="226" spans="1:3">
       <c r="A226">
-        <v>2004</v>
+        <v>2001</v>
       </c>
       <c r="B226" t="s">
         <v>12</v>
       </c>
+      <c r="C226">
+        <v>13</v>
+      </c>
     </row>
     <row r="227" spans="1:3">
       <c r="A227">
-        <v>2005</v>
+        <v>2002</v>
       </c>
       <c r="B227" t="s">
         <v>12</v>
       </c>
       <c r="C227">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="228" spans="1:3">
       <c r="A228">
-        <v>2007</v>
+        <v>2003</v>
       </c>
       <c r="B228" t="s">
         <v>12</v>
       </c>
       <c r="C228">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="229" spans="1:3">
       <c r="A229">
-        <v>2008</v>
+        <v>2004</v>
       </c>
       <c r="B229" t="s">
         <v>12</v>
       </c>
-      <c r="C229">
-        <v>14</v>
-      </c>
     </row>
     <row r="230" spans="1:3">
       <c r="A230">
-        <v>2009</v>
+        <v>2005</v>
       </c>
       <c r="B230" t="s">
         <v>12</v>
       </c>
       <c r="C230">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="231" spans="1:3">
       <c r="A231">
-        <v>2011</v>
+        <v>2007</v>
       </c>
       <c r="B231" t="s">
         <v>12</v>
       </c>
       <c r="C231">
-        <v>14.33333333333333</v>
+        <v>14</v>
       </c>
     </row>
     <row r="232" spans="1:3">
       <c r="A232">
-        <v>2012</v>
+        <v>2008</v>
       </c>
       <c r="B232" t="s">
         <v>12</v>
       </c>
       <c r="C232">
-        <v>13.66666666666667</v>
+        <v>14</v>
       </c>
     </row>
     <row r="233" spans="1:3">
       <c r="A233">
-        <v>2013</v>
+        <v>2009</v>
       </c>
       <c r="B233" t="s">
         <v>12</v>
       </c>
       <c r="C233">
-        <v>13.5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="234" spans="1:3">
       <c r="A234">
-        <v>2014</v>
+        <v>2011</v>
       </c>
       <c r="B234" t="s">
         <v>12</v>
       </c>
       <c r="C234">
-        <v>12</v>
+        <v>14.33333333333333</v>
       </c>
     </row>
     <row r="235" spans="1:3">
       <c r="A235">
-        <v>2015</v>
+        <v>2012</v>
       </c>
       <c r="B235" t="s">
         <v>12</v>
       </c>
       <c r="C235">
-        <v>12.33333333333333</v>
+        <v>13.66666666666667</v>
       </c>
     </row>
     <row r="236" spans="1:3">
       <c r="A236">
-        <v>2016</v>
+        <v>2013</v>
       </c>
       <c r="B236" t="s">
         <v>12</v>
       </c>
       <c r="C236">
-        <v>12.33333333333333</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="237" spans="1:3">
       <c r="A237">
-        <v>2017</v>
+        <v>2014</v>
       </c>
       <c r="B237" t="s">
         <v>12</v>
       </c>
       <c r="C237">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="238" spans="1:3">
       <c r="A238">
-        <v>2018</v>
+        <v>2015</v>
       </c>
       <c r="B238" t="s">
         <v>12</v>
       </c>
       <c r="C238">
-        <v>11.5</v>
+        <v>12.33333333333333</v>
       </c>
     </row>
     <row r="239" spans="1:3">
       <c r="A239">
-        <v>2019</v>
+        <v>2016</v>
       </c>
       <c r="B239" t="s">
         <v>12</v>
       </c>
       <c r="C239">
-        <v>11</v>
+        <v>12.33333333333333</v>
       </c>
     </row>
     <row r="240" spans="1:3">
       <c r="A240">
-        <v>2020</v>
+        <v>2017</v>
       </c>
       <c r="B240" t="s">
         <v>12</v>
       </c>
       <c r="C240">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="241" spans="1:3">
       <c r="A241">
-        <v>2021</v>
+        <v>2018</v>
       </c>
       <c r="B241" t="s">
         <v>12</v>
       </c>
       <c r="C241">
-        <v>9</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="242" spans="1:3">
       <c r="A242">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="B242" t="s">
         <v>12</v>
       </c>
       <c r="C242">
-        <v>9.333333333333334</v>
+        <v>11</v>
       </c>
     </row>
     <row r="243" spans="1:3">
       <c r="A243">
-        <v>2023</v>
+        <v>2020</v>
       </c>
       <c r="B243" t="s">
         <v>12</v>
@@ -2986,23 +2986,56 @@
     </row>
     <row r="244" spans="1:3">
       <c r="A244">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="B244" t="s">
         <v>12</v>
       </c>
       <c r="C244">
-        <v>9.5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="245" spans="1:3">
       <c r="A245">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="B245" t="s">
         <v>12</v>
       </c>
       <c r="C245">
+        <v>9.333333333333334</v>
+      </c>
+    </row>
+    <row r="246" spans="1:3">
+      <c r="A246">
+        <v>2023</v>
+      </c>
+      <c r="B246" t="s">
+        <v>12</v>
+      </c>
+      <c r="C246">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="247" spans="1:3">
+      <c r="A247">
+        <v>2024</v>
+      </c>
+      <c r="B247" t="s">
+        <v>12</v>
+      </c>
+      <c r="C247">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="248" spans="1:3">
+      <c r="A248">
+        <v>2025</v>
+      </c>
+      <c r="B248" t="s">
+        <v>12</v>
+      </c>
+      <c r="C248">
         <v>9</v>
       </c>
     </row>
